--- a/history_prices/APR/prices_06042026.xlsx
+++ b/history_prices/APR/prices_06042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\APR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC0BE8B-C363-4A59-8B1B-BBDF12C1A253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ECFE85C-812F-4B1D-9947-6B4E34788126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="194">
   <si>
     <t>ID</t>
   </si>
@@ -590,21 +590,40 @@
   </si>
   <si>
     <t>ОТСТЪПКА</t>
+  </si>
+  <si>
+    <t>АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ</t>
+  </si>
+  <si>
+    <t>0212</t>
+  </si>
+  <si>
+    <t>0213</t>
+  </si>
+  <si>
+    <t>000455464</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.000_-"/>
-    <numFmt numFmtId="167" formatCode="&quot;€&quot;#,##0.00_-"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="&quot;€&quot;#,##0.000_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.00_-"/>
+    <numFmt numFmtId="167" formatCode="[$€-2]\ #,##0.00;[Red]\-[$€-2]\ #,##0.00"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -630,12 +649,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -938,18 +959,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+    <col min="3" max="3" width="59.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="26.42578125" customWidth="1"/>
     <col min="6" max="6" width="23.28515625" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="28.140625" customWidth="1"/>
     <col min="9" max="9" width="27.42578125" customWidth="1"/>
-    <col min="10" max="13" width="23.28515625" customWidth="1"/>
+    <col min="10" max="12" width="23.28515625" customWidth="1"/>
+    <col min="13" max="13" width="23.28515625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -989,7 +1011,7 @@
       <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1024,7 +1046,7 @@
       <c r="J2" t="s">
         <v>16</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1059,7 +1081,7 @@
       <c r="J3" t="s">
         <v>16</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1094,7 +1116,7 @@
       <c r="J4" t="s">
         <v>22</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="6" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1129,7 +1151,7 @@
       <c r="J5" t="s">
         <v>22</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="6" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1167,7 +1189,7 @@
       <c r="K6" t="s">
         <v>28</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1205,7 +1227,7 @@
       <c r="K7" t="s">
         <v>28</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1240,7 +1262,7 @@
       <c r="J8" t="s">
         <v>33</v>
       </c>
-      <c r="M8" t="s">
+      <c r="M8" s="6" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1275,7 +1297,7 @@
       <c r="J9" t="s">
         <v>33</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M9" s="6" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1310,7 +1332,7 @@
       <c r="J10" t="s">
         <v>38</v>
       </c>
-      <c r="M10" t="s">
+      <c r="M10" s="6" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1351,7 +1373,7 @@
       <c r="L11" t="s">
         <v>44</v>
       </c>
-      <c r="M11" t="s">
+      <c r="M11" s="6" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1392,7 +1414,7 @@
       <c r="L12" t="s">
         <v>44</v>
       </c>
-      <c r="M12" t="s">
+      <c r="M12" s="6" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1427,7 +1449,7 @@
       <c r="J13" t="s">
         <v>49</v>
       </c>
-      <c r="M13" t="s">
+      <c r="M13" s="6" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1462,7 +1484,7 @@
       <c r="J14" t="s">
         <v>49</v>
       </c>
-      <c r="M14" t="s">
+      <c r="M14" s="6" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1497,7 +1519,7 @@
       <c r="J15" t="s">
         <v>54</v>
       </c>
-      <c r="M15" t="s">
+      <c r="M15" s="6" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1532,7 +1554,7 @@
       <c r="J16" t="s">
         <v>54</v>
       </c>
-      <c r="M16" t="s">
+      <c r="M16" s="6" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1567,7 +1589,7 @@
       <c r="J17" t="s">
         <v>59</v>
       </c>
-      <c r="M17" t="s">
+      <c r="M17" s="6" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1602,7 +1624,7 @@
       <c r="J18" t="s">
         <v>59</v>
       </c>
-      <c r="M18" t="s">
+      <c r="M18" s="6" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1640,7 +1662,7 @@
       <c r="K19" t="s">
         <v>65</v>
       </c>
-      <c r="M19" t="s">
+      <c r="M19" s="6" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1678,7 +1700,7 @@
       <c r="K20" t="s">
         <v>65</v>
       </c>
-      <c r="M20" t="s">
+      <c r="M20" s="6" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1716,7 +1738,7 @@
       <c r="K21" t="s">
         <v>65</v>
       </c>
-      <c r="M21" t="s">
+      <c r="M21" s="6" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1754,7 +1776,7 @@
       <c r="K22" t="s">
         <v>65</v>
       </c>
-      <c r="M22" t="s">
+      <c r="M22" s="6" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1792,7 +1814,7 @@
       <c r="K23" t="s">
         <v>75</v>
       </c>
-      <c r="M23" t="s">
+      <c r="M23" s="6" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1830,7 +1852,7 @@
       <c r="K24" t="s">
         <v>75</v>
       </c>
-      <c r="M24" t="s">
+      <c r="M24" s="6" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1868,7 +1890,7 @@
       <c r="K25" t="s">
         <v>75</v>
       </c>
-      <c r="M25" t="s">
+      <c r="M25" s="6" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1906,7 +1928,7 @@
       <c r="K26" t="s">
         <v>75</v>
       </c>
-      <c r="M26" t="s">
+      <c r="M26" s="6" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1941,7 +1963,7 @@
       <c r="J27" t="s">
         <v>82</v>
       </c>
-      <c r="M27" t="s">
+      <c r="M27" s="6" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1976,7 +1998,7 @@
       <c r="J28" t="s">
         <v>82</v>
       </c>
-      <c r="M28" t="s">
+      <c r="M28" s="6" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2014,7 +2036,7 @@
       <c r="K29" t="s">
         <v>88</v>
       </c>
-      <c r="M29" t="s">
+      <c r="M29" s="6" t="s">
         <v>89</v>
       </c>
     </row>
@@ -2052,7 +2074,7 @@
       <c r="K30" t="s">
         <v>88</v>
       </c>
-      <c r="M30" t="s">
+      <c r="M30" s="6" t="s">
         <v>89</v>
       </c>
     </row>
@@ -2087,7 +2109,7 @@
       <c r="J31" t="s">
         <v>93</v>
       </c>
-      <c r="M31" t="s">
+      <c r="M31" s="6" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2122,7 +2144,7 @@
       <c r="J32" t="s">
         <v>93</v>
       </c>
-      <c r="M32" t="s">
+      <c r="M32" s="6" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2157,7 +2179,7 @@
       <c r="J33" t="s">
         <v>98</v>
       </c>
-      <c r="M33" t="s">
+      <c r="M33" s="6" t="s">
         <v>99</v>
       </c>
     </row>
@@ -2195,7 +2217,7 @@
       <c r="K34" t="s">
         <v>103</v>
       </c>
-      <c r="M34" t="s">
+      <c r="M34" s="6" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2233,7 +2255,7 @@
       <c r="K35" t="s">
         <v>103</v>
       </c>
-      <c r="M35" t="s">
+      <c r="M35" s="6" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2268,7 +2290,7 @@
       <c r="J36" t="s">
         <v>108</v>
       </c>
-      <c r="M36" t="s">
+      <c r="M36" s="6" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2303,7 +2325,7 @@
       <c r="J37" t="s">
         <v>112</v>
       </c>
-      <c r="M37" t="s">
+      <c r="M37" s="6" t="s">
         <v>113</v>
       </c>
     </row>
@@ -2338,7 +2360,7 @@
       <c r="J38" t="s">
         <v>112</v>
       </c>
-      <c r="M38" t="s">
+      <c r="M38" s="6" t="s">
         <v>113</v>
       </c>
     </row>
@@ -2376,7 +2398,7 @@
       <c r="K39" t="s">
         <v>118</v>
       </c>
-      <c r="M39" t="s">
+      <c r="M39" s="6" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2414,7 +2436,7 @@
       <c r="K40" t="s">
         <v>118</v>
       </c>
-      <c r="M40" t="s">
+      <c r="M40" s="6" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2452,7 +2474,7 @@
       <c r="K41" t="s">
         <v>118</v>
       </c>
-      <c r="M41" t="s">
+      <c r="M41" s="6" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2490,7 +2512,7 @@
       <c r="K42" t="s">
         <v>118</v>
       </c>
-      <c r="M42" t="s">
+      <c r="M42" s="6" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2525,7 +2547,7 @@
       <c r="J43" t="s">
         <v>125</v>
       </c>
-      <c r="M43" t="s">
+      <c r="M43" s="6" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2560,7 +2582,7 @@
       <c r="J44" t="s">
         <v>125</v>
       </c>
-      <c r="M44" t="s">
+      <c r="M44" s="6" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2598,7 +2620,7 @@
       <c r="K45" t="s">
         <v>131</v>
       </c>
-      <c r="M45" t="s">
+      <c r="M45" s="6" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2636,7 +2658,7 @@
       <c r="K46" t="s">
         <v>131</v>
       </c>
-      <c r="M46" t="s">
+      <c r="M46" s="6" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2674,7 +2696,7 @@
       <c r="K47" t="s">
         <v>131</v>
       </c>
-      <c r="M47" t="s">
+      <c r="M47" s="6" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2712,7 +2734,7 @@
       <c r="K48" t="s">
         <v>131</v>
       </c>
-      <c r="M48" t="s">
+      <c r="M48" s="6" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2750,7 +2772,7 @@
       <c r="K49" t="s">
         <v>139</v>
       </c>
-      <c r="M49" t="s">
+      <c r="M49" s="6" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2788,7 +2810,7 @@
       <c r="K50" t="s">
         <v>139</v>
       </c>
-      <c r="M50" t="s">
+      <c r="M50" s="6" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2826,7 +2848,7 @@
       <c r="K51" t="s">
         <v>139</v>
       </c>
-      <c r="M51" t="s">
+      <c r="M51" s="6" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2864,7 +2886,7 @@
       <c r="K52" t="s">
         <v>139</v>
       </c>
-      <c r="M52" t="s">
+      <c r="M52" s="6" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2893,7 +2915,7 @@
       <c r="H53" s="3">
         <v>1.734</v>
       </c>
-      <c r="M53" t="s">
+      <c r="M53" s="6" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2922,7 +2944,7 @@
       <c r="H54" s="3">
         <v>1.734</v>
       </c>
-      <c r="M54" t="s">
+      <c r="M54" s="6" t="s">
         <v>149</v>
       </c>
     </row>
@@ -2951,7 +2973,7 @@
       <c r="H55" s="3">
         <v>1.734</v>
       </c>
-      <c r="M55" t="s">
+      <c r="M55" s="6" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2980,7 +3002,7 @@
       <c r="H56" s="3">
         <v>1.734</v>
       </c>
-      <c r="M56" t="s">
+      <c r="M56" s="6" t="s">
         <v>155</v>
       </c>
     </row>
@@ -3009,7 +3031,7 @@
       <c r="H57" s="3">
         <v>1.734</v>
       </c>
-      <c r="M57" t="s">
+      <c r="M57" s="6" t="s">
         <v>158</v>
       </c>
     </row>
@@ -3038,7 +3060,7 @@
       <c r="H58" s="3">
         <v>1.4390000000000001</v>
       </c>
-      <c r="M58" t="s">
+      <c r="M58" s="6" t="s">
         <v>152</v>
       </c>
     </row>
@@ -3067,7 +3089,7 @@
       <c r="H59" s="3">
         <v>1.429</v>
       </c>
-      <c r="M59" t="s">
+      <c r="M59" s="6" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3096,7 +3118,7 @@
       <c r="H60" s="3">
         <v>1.734</v>
       </c>
-      <c r="M60" t="s">
+      <c r="M60" s="6" t="s">
         <v>163</v>
       </c>
     </row>
@@ -3125,7 +3147,7 @@
       <c r="H61" s="3">
         <v>1.429</v>
       </c>
-      <c r="M61" t="s">
+      <c r="M61" s="6" t="s">
         <v>163</v>
       </c>
     </row>
@@ -3154,7 +3176,7 @@
       <c r="H62" s="3">
         <v>1.419</v>
       </c>
-      <c r="M62" t="s">
+      <c r="M62" s="6" t="s">
         <v>158</v>
       </c>
     </row>
@@ -3183,7 +3205,7 @@
       <c r="H63" s="3">
         <v>1.419</v>
       </c>
-      <c r="M63" t="s">
+      <c r="M63" s="6" t="s">
         <v>155</v>
       </c>
     </row>
@@ -3212,7 +3234,7 @@
       <c r="H64" s="3">
         <v>1.429</v>
       </c>
-      <c r="M64" t="s">
+      <c r="M64" s="6" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3247,7 +3269,7 @@
       <c r="J65" t="s">
         <v>170</v>
       </c>
-      <c r="M65" t="s">
+      <c r="M65" s="6" t="s">
         <v>171</v>
       </c>
     </row>
@@ -3282,7 +3304,7 @@
       <c r="J66" t="s">
         <v>170</v>
       </c>
-      <c r="M66" t="s">
+      <c r="M66" s="6" t="s">
         <v>171</v>
       </c>
     </row>
@@ -3311,7 +3333,7 @@
       <c r="H67" s="3">
         <v>1.734</v>
       </c>
-      <c r="M67" t="s">
+      <c r="M67" s="6" t="s">
         <v>175</v>
       </c>
     </row>
@@ -3340,7 +3362,7 @@
       <c r="H68" s="3">
         <v>1.429</v>
       </c>
-      <c r="M68" t="s">
+      <c r="M68" s="6" t="s">
         <v>175</v>
       </c>
     </row>
@@ -3369,7 +3391,7 @@
       <c r="H69" s="3">
         <v>1.724</v>
       </c>
-      <c r="M69" t="s">
+      <c r="M69" s="6" t="s">
         <v>179</v>
       </c>
     </row>
@@ -3398,7 +3420,7 @@
       <c r="H70" s="3">
         <v>1.724</v>
       </c>
-      <c r="M70" t="s">
+      <c r="M70" s="6" t="s">
         <v>179</v>
       </c>
     </row>
@@ -3427,7 +3449,7 @@
       <c r="H71" s="3">
         <v>1.399</v>
       </c>
-      <c r="M71" t="s">
+      <c r="M71" s="6" t="s">
         <v>179</v>
       </c>
     </row>
@@ -3456,7 +3478,7 @@
       <c r="H72" s="3">
         <v>1.625</v>
       </c>
-      <c r="M72" t="s">
+      <c r="M72" s="6" t="s">
         <v>179</v>
       </c>
     </row>
@@ -3485,7 +3507,7 @@
       <c r="H73" s="3">
         <v>1.724</v>
       </c>
-      <c r="M73" t="s">
+      <c r="M73" s="6" t="s">
         <v>185</v>
       </c>
     </row>
@@ -3514,7 +3536,7 @@
       <c r="H74" s="3">
         <v>1.724</v>
       </c>
-      <c r="M74" t="s">
+      <c r="M74" s="6" t="s">
         <v>185</v>
       </c>
     </row>
@@ -3543,7 +3565,7 @@
       <c r="H75" s="3">
         <v>1.399</v>
       </c>
-      <c r="M75" t="s">
+      <c r="M75" s="6" t="s">
         <v>185</v>
       </c>
     </row>
@@ -3572,11 +3594,70 @@
       <c r="H76" s="3">
         <v>1.625</v>
       </c>
-      <c r="M76" t="s">
+      <c r="M76" s="6" t="s">
         <v>185</v>
       </c>
     </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>191</v>
+      </c>
+      <c r="B77" s="1">
+        <v>46118</v>
+      </c>
+      <c r="C77" t="s">
+        <v>190</v>
+      </c>
+      <c r="D77" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77">
+        <v>0.04</v>
+      </c>
+      <c r="F77" s="5">
+        <v>1.724</v>
+      </c>
+      <c r="G77" s="5">
+        <v>0</v>
+      </c>
+      <c r="H77" s="2">
+        <v>1.724</v>
+      </c>
+      <c r="M77" s="6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>192</v>
+      </c>
+      <c r="B78" s="1">
+        <v>46118</v>
+      </c>
+      <c r="C78" t="s">
+        <v>190</v>
+      </c>
+      <c r="D78" t="s">
+        <v>19</v>
+      </c>
+      <c r="E78">
+        <v>0.04</v>
+      </c>
+      <c r="F78" s="5">
+        <v>1.399</v>
+      </c>
+      <c r="G78" s="5">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2">
+        <v>1.399</v>
+      </c>
+      <c r="M78" s="6" t="s">
+        <v>193</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/history_prices/APR/prices_06042026.xlsx
+++ b/history_prices/APR/prices_06042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\APR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ECFE85C-812F-4B1D-9947-6B4E34788126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3F86E6-92B3-43FE-80C3-7F71A4DDEB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
